--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/176.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/176.xlsx
@@ -426,13 +426,13 @@
         <v>6.394747456153546</v>
       </c>
       <c r="E2">
-        <v>-12.85084674551244</v>
+        <v>-12.41932845732153</v>
       </c>
       <c r="F2">
-        <v>-2.666858589331278</v>
+        <v>-2.714774673378813</v>
       </c>
       <c r="G2">
-        <v>-6.823843280217832</v>
+        <v>-5.947965625801776</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.297129986221836</v>
       </c>
       <c r="E3">
-        <v>-12.29328744026605</v>
+        <v>-12.70307358169414</v>
       </c>
       <c r="F3">
-        <v>-3.048904948972021</v>
+        <v>-2.822091327146294</v>
       </c>
       <c r="G3">
-        <v>-7.01104800937254</v>
+        <v>-6.53559739065903</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>6.150866180082311</v>
       </c>
       <c r="E4">
-        <v>-13.2175082289655</v>
+        <v>-12.52731444850844</v>
       </c>
       <c r="F4">
-        <v>-2.994081937519944</v>
+        <v>-2.679694970605059</v>
       </c>
       <c r="G4">
-        <v>-6.542758100660473</v>
+        <v>-5.706017715609681</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.976745667804737</v>
       </c>
       <c r="E5">
-        <v>-15.11657814577015</v>
+        <v>-14.07779149315065</v>
       </c>
       <c r="F5">
-        <v>-3.22003405724676</v>
+        <v>-2.739006905012907</v>
       </c>
       <c r="G5">
-        <v>-6.474127181085843</v>
+        <v>-5.323441141454884</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.789919714059026</v>
       </c>
       <c r="E6">
-        <v>-13.77787971657066</v>
+        <v>-13.91484794140665</v>
       </c>
       <c r="F6">
-        <v>-3.389741687058295</v>
+        <v>-2.681750150131405</v>
       </c>
       <c r="G6">
-        <v>-6.251526099025248</v>
+        <v>-5.624296898972771</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.616635041657876</v>
       </c>
       <c r="E7">
-        <v>-14.98619885061531</v>
+        <v>-15.32357922113477</v>
       </c>
       <c r="F7">
-        <v>-3.46886319953669</v>
+        <v>-2.46960774337666</v>
       </c>
       <c r="G7">
-        <v>-6.122444617903525</v>
+        <v>-4.413736332718555</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.482037703557997</v>
       </c>
       <c r="E8">
-        <v>-15.97616855343213</v>
+        <v>-15.14259422894422</v>
       </c>
       <c r="F8">
-        <v>-3.21693596316029</v>
+        <v>-2.876847240838744</v>
       </c>
       <c r="G8">
-        <v>-5.540096483726948</v>
+        <v>-4.871799966259813</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.40371367842243</v>
       </c>
       <c r="E9">
-        <v>-16.43871141704959</v>
+        <v>-15.75438653890648</v>
       </c>
       <c r="F9">
-        <v>-3.69515992010307</v>
+        <v>-3.046003177960015</v>
       </c>
       <c r="G9">
-        <v>-6.219817693850108</v>
+        <v>-3.954308754415118</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.391627679080894</v>
       </c>
       <c r="E10">
-        <v>-15.64126072972086</v>
+        <v>-16.41565695587654</v>
       </c>
       <c r="F10">
-        <v>-3.452312418828755</v>
+        <v>-3.220426703395687</v>
       </c>
       <c r="G10">
-        <v>-5.02957063502486</v>
+        <v>-3.653635076901891</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.459516539372188</v>
       </c>
       <c r="E11">
-        <v>-16.95870250192835</v>
+        <v>-16.63959905250385</v>
       </c>
       <c r="F11">
-        <v>-3.409475055327785</v>
+        <v>-2.843834314734976</v>
       </c>
       <c r="G11">
-        <v>-4.236310955086855</v>
+        <v>-3.508610008463037</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.605142198441253</v>
       </c>
       <c r="E12">
-        <v>-17.20109813013693</v>
+        <v>-17.87153417849851</v>
       </c>
       <c r="F12">
-        <v>-3.295993691348669</v>
+        <v>-3.277405955197251</v>
       </c>
       <c r="G12">
-        <v>-4.262239147750427</v>
+        <v>-3.112930295063806</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.809119711095525</v>
       </c>
       <c r="E13">
-        <v>-18.76661423695861</v>
+        <v>-18.43312382561174</v>
       </c>
       <c r="F13">
-        <v>-3.181604436696085</v>
+        <v>-3.09003421888842</v>
       </c>
       <c r="G13">
-        <v>-2.792390033769413</v>
+        <v>-2.431755755448906</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.059181091077218</v>
       </c>
       <c r="E14">
-        <v>-19.45065834971324</v>
+        <v>-18.43101355672416</v>
       </c>
       <c r="F14">
-        <v>-3.782315768021217</v>
+        <v>-2.762716436815834</v>
       </c>
       <c r="G14">
-        <v>-3.203222114101888</v>
+        <v>-2.518594675489529</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.333052747783584</v>
       </c>
       <c r="E15">
-        <v>-20.12935433466482</v>
+        <v>-19.03978990299731</v>
       </c>
       <c r="F15">
-        <v>-3.482871720685432</v>
+        <v>-3.159588916231883</v>
       </c>
       <c r="G15">
-        <v>-3.35038910550465</v>
+        <v>-1.737375449677853</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.602915257327926</v>
       </c>
       <c r="E16">
-        <v>-20.39186091594146</v>
+        <v>-20.20577233354426</v>
       </c>
       <c r="F16">
-        <v>-3.176845465967002</v>
+        <v>-2.733798959151506</v>
       </c>
       <c r="G16">
-        <v>-2.540861404786666</v>
+        <v>-0.7586292137200228</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.847263365523575</v>
       </c>
       <c r="E17">
-        <v>-20.93752844844371</v>
+        <v>-20.76058738354201</v>
       </c>
       <c r="F17">
-        <v>-3.160820698559846</v>
+        <v>-2.835336921917059</v>
       </c>
       <c r="G17">
-        <v>-1.963548610375321</v>
+        <v>-0.6579654555074038</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.054129556259392</v>
       </c>
       <c r="E18">
-        <v>-21.89910914770645</v>
+        <v>-22.51322456483464</v>
       </c>
       <c r="F18">
-        <v>-2.777813432731855</v>
+        <v>-2.721652607924257</v>
       </c>
       <c r="G18">
-        <v>-0.973010211206607</v>
+        <v>-0.431113632974385</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.210300327096082</v>
       </c>
       <c r="E19">
-        <v>-22.33990627913907</v>
+        <v>-21.49666366264478</v>
       </c>
       <c r="F19">
-        <v>-2.966878352012009</v>
+        <v>-2.563045929677639</v>
       </c>
       <c r="G19">
-        <v>-1.961744363056418</v>
+        <v>-0.5521206935258254</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.303763989670866</v>
       </c>
       <c r="E20">
-        <v>-23.37407388827075</v>
+        <v>-23.21985217746553</v>
       </c>
       <c r="F20">
-        <v>-2.924624987530012</v>
+        <v>-2.107327886701519</v>
       </c>
       <c r="G20">
-        <v>-0.9463404563422384</v>
+        <v>-0.1918307119414029</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.336605564988113</v>
       </c>
       <c r="E21">
-        <v>-22.79570624495911</v>
+        <v>-23.02659502071419</v>
       </c>
       <c r="F21">
-        <v>-2.485075019521732</v>
+        <v>-2.120291008187928</v>
       </c>
       <c r="G21">
-        <v>-0.4337951748611946</v>
+        <v>-0.3374318153040889</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.309083595079641</v>
       </c>
       <c r="E22">
-        <v>-23.70083045876821</v>
+        <v>-24.52363607206589</v>
       </c>
       <c r="F22">
-        <v>-2.221472772970276</v>
+        <v>-1.964451905434063</v>
       </c>
       <c r="G22">
-        <v>-0.7958463666725095</v>
+        <v>0.1254354198146514</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.218011903924015</v>
       </c>
       <c r="E23">
-        <v>-24.07956485392571</v>
+        <v>-23.59929301456823</v>
       </c>
       <c r="F23">
-        <v>-2.391779312414035</v>
+        <v>-1.71147347082351</v>
       </c>
       <c r="G23">
-        <v>-1.15173994378078</v>
+        <v>0.9652479911258876</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.07132950783363</v>
       </c>
       <c r="E24">
-        <v>-24.99567514567743</v>
+        <v>-23.85942667546484</v>
       </c>
       <c r="F24">
-        <v>-1.711626718793028</v>
+        <v>-1.657316466763284</v>
       </c>
       <c r="G24">
-        <v>-0.4636364323521851</v>
+        <v>0.2568607671781782</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.875995990633672</v>
       </c>
       <c r="E25">
-        <v>-25.54911353957685</v>
+        <v>-25.22989234982815</v>
       </c>
       <c r="F25">
-        <v>-2.206523226451954</v>
+        <v>-1.818428128035968</v>
       </c>
       <c r="G25">
-        <v>-0.6388735393824269</v>
+        <v>0.3606066432878587</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.635379834125759</v>
       </c>
       <c r="E26">
-        <v>-26.92787084984819</v>
+        <v>-25.16762130374867</v>
       </c>
       <c r="F26">
-        <v>-1.827010842696374</v>
+        <v>-1.610216324607507</v>
       </c>
       <c r="G26">
-        <v>-0.4682414011973113</v>
+        <v>-0.30349541298102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.357473264644384</v>
       </c>
       <c r="E27">
-        <v>-24.9452958723421</v>
+        <v>-24.98331694011049</v>
       </c>
       <c r="F27">
-        <v>-2.301177456100242</v>
+        <v>-1.338203663815428</v>
       </c>
       <c r="G27">
-        <v>-2.341126260765818</v>
+        <v>0.2022069708703502</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.053625522804537</v>
       </c>
       <c r="E28">
-        <v>-25.20509895463615</v>
+        <v>-23.59594194380255</v>
       </c>
       <c r="F28">
-        <v>-1.932792531666468</v>
+        <v>-1.951397663533345</v>
       </c>
       <c r="G28">
-        <v>-0.8229464924569834</v>
+        <v>-0.3779562032503075</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.729818598503925</v>
       </c>
       <c r="E29">
-        <v>-24.64422933489015</v>
+        <v>-24.62411385334807</v>
       </c>
       <c r="F29">
-        <v>-2.056804102069971</v>
+        <v>-1.541918260614091</v>
       </c>
       <c r="G29">
-        <v>-0.7987596467470681</v>
+        <v>-0.3769497974063691</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.388802184984551</v>
       </c>
       <c r="E30">
-        <v>-25.98453990083637</v>
+        <v>-23.79813377977102</v>
       </c>
       <c r="F30">
-        <v>-1.473224237002136</v>
+        <v>-1.796960158425017</v>
       </c>
       <c r="G30">
-        <v>-1.356215789013865</v>
+        <v>-1.067112468160391</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.042442311900153</v>
       </c>
       <c r="E31">
-        <v>-25.36457822376428</v>
+        <v>-23.28008993871556</v>
       </c>
       <c r="F31">
-        <v>-1.374453849729337</v>
+        <v>-1.405685785917087</v>
       </c>
       <c r="G31">
-        <v>-1.648877946322056</v>
+        <v>-1.016656443596358</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.6952217167901</v>
       </c>
       <c r="E32">
-        <v>-25.7724307067911</v>
+        <v>-23.66814846185486</v>
       </c>
       <c r="F32">
-        <v>-1.885785166659805</v>
+        <v>-1.255963348065493</v>
       </c>
       <c r="G32">
-        <v>-1.418228928055493</v>
+        <v>-0.4597068147970702</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.347363487659202</v>
       </c>
       <c r="E33">
-        <v>-23.96079203765254</v>
+        <v>-23.9118845183697</v>
       </c>
       <c r="F33">
-        <v>-1.767670743796832</v>
+        <v>-1.538835905508274</v>
       </c>
       <c r="G33">
-        <v>-0.9098582444994698</v>
+        <v>-0.7268910136350299</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.008206028049223</v>
       </c>
       <c r="E34">
-        <v>-23.53401053327365</v>
+        <v>-22.48855796691486</v>
       </c>
       <c r="F34">
-        <v>-1.783308663626881</v>
+        <v>-1.568602459760471</v>
       </c>
       <c r="G34">
-        <v>-1.393840139067682</v>
+        <v>-1.139341950736209</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.683586711538484</v>
       </c>
       <c r="E35">
-        <v>-24.18793123692927</v>
+        <v>-22.54706132261995</v>
       </c>
       <c r="F35">
-        <v>-1.218983370469717</v>
+        <v>-1.416257410711614</v>
       </c>
       <c r="G35">
-        <v>-2.436877169398158</v>
+        <v>-0.6297231915118813</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.3753883654337</v>
       </c>
       <c r="E36">
-        <v>-23.18468404832196</v>
+        <v>-21.85973859468376</v>
       </c>
       <c r="F36">
-        <v>-1.4075835756369</v>
+        <v>-1.39582738545637</v>
       </c>
       <c r="G36">
-        <v>-1.527066423204572</v>
+        <v>-1.528089381776207</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.088317634031486</v>
       </c>
       <c r="E37">
-        <v>-22.68161134233585</v>
+        <v>-22.31085158990586</v>
       </c>
       <c r="F37">
-        <v>-1.435853269992239</v>
+        <v>-1.273366518830908</v>
       </c>
       <c r="G37">
-        <v>-2.655154678984465</v>
+        <v>-1.349935684125867</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.830368131137182</v>
       </c>
       <c r="E38">
-        <v>-22.26973757439022</v>
+        <v>-21.19541145775852</v>
       </c>
       <c r="F38">
-        <v>-0.9197348178409932</v>
+        <v>-1.100030639795111</v>
       </c>
       <c r="G38">
-        <v>-1.769739342869768</v>
+        <v>-0.9162740817545775</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.605060357490253</v>
       </c>
       <c r="E39">
-        <v>-21.06342455433096</v>
+        <v>-20.90318450156954</v>
       </c>
       <c r="F39">
-        <v>-1.477359447076911</v>
+        <v>-0.7944699275570548</v>
       </c>
       <c r="G39">
-        <v>-2.25844538592252</v>
+        <v>-0.4372447633131152</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.412764100957054</v>
       </c>
       <c r="E40">
-        <v>-21.21990597366601</v>
+        <v>-21.09890967665506</v>
       </c>
       <c r="F40">
-        <v>-1.670713652768761</v>
+        <v>-1.270965081730192</v>
       </c>
       <c r="G40">
-        <v>-1.960344002293307</v>
+        <v>-1.239462779480388</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.261461355978932</v>
       </c>
       <c r="E41">
-        <v>-19.33707063617885</v>
+        <v>-19.53738315543414</v>
       </c>
       <c r="F41">
-        <v>-0.9816188330345331</v>
+        <v>-1.044905274241013</v>
       </c>
       <c r="G41">
-        <v>-2.213971517147951</v>
+        <v>-0.9006714806279923</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.151588738470067</v>
       </c>
       <c r="E42">
-        <v>-20.50351949954859</v>
+        <v>-18.633418230971</v>
       </c>
       <c r="F42">
-        <v>-1.752341805008027</v>
+        <v>-1.11476895262572</v>
       </c>
       <c r="G42">
-        <v>-2.160519448870878</v>
+        <v>-1.424853329679574</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.078235539182177</v>
       </c>
       <c r="E43">
-        <v>-20.02382277639007</v>
+        <v>-19.42048059892613</v>
       </c>
       <c r="F43">
-        <v>-1.466217077141855</v>
+        <v>-0.9930892364610978</v>
       </c>
       <c r="G43">
-        <v>-2.572357935047292</v>
+        <v>-1.610161116240279</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.038999246289206</v>
       </c>
       <c r="E44">
-        <v>-18.99970837955542</v>
+        <v>-18.67038869276962</v>
       </c>
       <c r="F44">
-        <v>-1.117814859565814</v>
+        <v>-1.041198330113485</v>
       </c>
       <c r="G44">
-        <v>-2.173318017925701</v>
+        <v>-0.7609300428698162</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.029151470435875</v>
       </c>
       <c r="E45">
-        <v>-18.47073280224544</v>
+        <v>-17.64735207274879</v>
       </c>
       <c r="F45">
-        <v>-1.118528083899624</v>
+        <v>-0.9327393576975427</v>
       </c>
       <c r="G45">
-        <v>-1.487505404010282</v>
+        <v>-1.759354161513074</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.040366627895346</v>
       </c>
       <c r="E46">
-        <v>-17.53600595384819</v>
+        <v>-16.55217686178578</v>
       </c>
       <c r="F46">
-        <v>-1.075851423674796</v>
+        <v>-1.04564417796431</v>
       </c>
       <c r="G46">
-        <v>-2.224121649771356</v>
+        <v>-0.891756181490735</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.064094786109392</v>
       </c>
       <c r="E47">
-        <v>-16.02563307501791</v>
+        <v>-16.90190185245014</v>
       </c>
       <c r="F47">
-        <v>-1.134785622546967</v>
+        <v>-1.330309322466749</v>
       </c>
       <c r="G47">
-        <v>-2.329963101207395</v>
+        <v>-1.724451079892538</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.095911727553347</v>
       </c>
       <c r="E48">
-        <v>-15.93360995470805</v>
+        <v>-16.18097331890303</v>
       </c>
       <c r="F48">
-        <v>-0.8629311799288227</v>
+        <v>-1.151112744056145</v>
       </c>
       <c r="G48">
-        <v>-2.682781181509683</v>
+        <v>-1.60066316108811</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.128751538754244</v>
       </c>
       <c r="E49">
-        <v>-16.77195276232604</v>
+        <v>-15.66421556446574</v>
       </c>
       <c r="F49">
-        <v>-1.171275206640286</v>
+        <v>-0.9085576564750195</v>
       </c>
       <c r="G49">
-        <v>-2.225806717450845</v>
+        <v>-1.511069867158814</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.153668654245727</v>
       </c>
       <c r="E50">
-        <v>-13.86090928750129</v>
+        <v>-14.57016794353064</v>
       </c>
       <c r="F50">
-        <v>-0.8165160976151609</v>
+        <v>-0.7804605780409095</v>
       </c>
       <c r="G50">
-        <v>-3.055628062324561</v>
+        <v>-1.261911588782186</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.167106861475198</v>
       </c>
       <c r="E51">
-        <v>-15.62883006856981</v>
+        <v>-15.09329726089672</v>
       </c>
       <c r="F51">
-        <v>-1.461367814365867</v>
+        <v>-1.167154907178761</v>
       </c>
       <c r="G51">
-        <v>-3.20803233677045</v>
+        <v>-2.405549476960035</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.164526921849123</v>
       </c>
       <c r="E52">
-        <v>-14.04728316376097</v>
+        <v>-13.83457168267268</v>
       </c>
       <c r="F52">
-        <v>-0.9100743971895454</v>
+        <v>-0.8810873366633823</v>
       </c>
       <c r="G52">
-        <v>-2.763485660666036</v>
+        <v>-1.863742283457373</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.141650177247592</v>
       </c>
       <c r="E53">
-        <v>-12.56956963947401</v>
+        <v>-12.8054216227415</v>
       </c>
       <c r="F53">
-        <v>-0.6824100420411433</v>
+        <v>-1.051940598592989</v>
       </c>
       <c r="G53">
-        <v>-3.242339520193917</v>
+        <v>-1.700608530918707</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.097414289189993</v>
       </c>
       <c r="E54">
-        <v>-13.59066807261956</v>
+        <v>-12.7760227694837</v>
       </c>
       <c r="F54">
-        <v>-0.8267356662634984</v>
+        <v>-1.014824768743154</v>
       </c>
       <c r="G54">
-        <v>-3.65999463488283</v>
+        <v>-1.929618829143331</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.032473645791701</v>
       </c>
       <c r="E55">
-        <v>-12.98712664229928</v>
+        <v>-13.62295609229425</v>
       </c>
       <c r="F55">
-        <v>-1.132803339352068</v>
+        <v>-0.7418578287030498</v>
       </c>
       <c r="G55">
-        <v>-3.099257741986616</v>
+        <v>-3.03355665521424</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.947129690683326</v>
       </c>
       <c r="E56">
-        <v>-12.87444915204042</v>
+        <v>-12.65528912396521</v>
       </c>
       <c r="F56">
-        <v>-0.7759608863089027</v>
+        <v>-1.02681041669426</v>
       </c>
       <c r="G56">
-        <v>-4.536829036959737</v>
+        <v>-2.732356600960269</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.842505906170561</v>
       </c>
       <c r="E57">
-        <v>-12.92789420227895</v>
+        <v>-11.57009919818911</v>
       </c>
       <c r="F57">
-        <v>-0.8619553631283249</v>
+        <v>-0.9412707135789747</v>
       </c>
       <c r="G57">
-        <v>-4.176257659004476</v>
+        <v>-3.242985076574075</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.722271972662347</v>
       </c>
       <c r="E58">
-        <v>-10.66328133510113</v>
+        <v>-12.39995564551672</v>
       </c>
       <c r="F58">
-        <v>-1.130116115497386</v>
+        <v>-0.9186745075654099</v>
       </c>
       <c r="G58">
-        <v>-3.517310122140242</v>
+        <v>-2.736600720341615</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.588425231633662</v>
       </c>
       <c r="E59">
-        <v>-11.26060064213487</v>
+        <v>-11.15637781284834</v>
       </c>
       <c r="F59">
-        <v>-1.118820497592812</v>
+        <v>-1.023261690740667</v>
       </c>
       <c r="G59">
-        <v>-3.747260615298019</v>
+        <v>-2.963641243970372</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.441947093895684</v>
       </c>
       <c r="E60">
-        <v>-10.66122540790165</v>
+        <v>-12.11416365089264</v>
       </c>
       <c r="F60">
-        <v>-0.8675484998320272</v>
+        <v>-0.9014055323192486</v>
       </c>
       <c r="G60">
-        <v>-4.288859244431706</v>
+        <v>-3.110838030282987</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.286181082066162</v>
       </c>
       <c r="E61">
-        <v>-11.03841559342253</v>
+        <v>-11.1796134129817</v>
       </c>
       <c r="F61">
-        <v>-1.244343010139022</v>
+        <v>-0.8486186479432529</v>
       </c>
       <c r="G61">
-        <v>-3.003791540270653</v>
+        <v>-3.758062925392661</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.122692701035708</v>
       </c>
       <c r="E62">
-        <v>-11.244732869212</v>
+        <v>-10.3436299403217</v>
       </c>
       <c r="F62">
-        <v>-0.3486608154532225</v>
+        <v>-0.9429199930779486</v>
       </c>
       <c r="G62">
-        <v>-4.711923790531789</v>
+        <v>-3.285297159111499</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.9524315244001681</v>
       </c>
       <c r="E63">
-        <v>-11.71440807939154</v>
+        <v>-9.788946216070176</v>
       </c>
       <c r="F63">
-        <v>-0.8212203960956592</v>
+        <v>-0.6369326716274504</v>
       </c>
       <c r="G63">
-        <v>-4.191714596127333</v>
+        <v>-3.264371200757767</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.7782843883742525</v>
       </c>
       <c r="E64">
-        <v>-10.91767289095602</v>
+        <v>-10.34157401312222</v>
       </c>
       <c r="F64">
-        <v>-0.8802158941556372</v>
+        <v>-0.9904384607721395</v>
       </c>
       <c r="G64">
-        <v>-3.805559322244584</v>
+        <v>-3.340089998331977</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6021512484841023</v>
       </c>
       <c r="E65">
-        <v>-10.40022227999556</v>
+        <v>-10.46086760390628</v>
       </c>
       <c r="F65">
-        <v>-1.299244716494364</v>
+        <v>-0.627642531205054</v>
       </c>
       <c r="G65">
-        <v>-4.708308674802905</v>
+        <v>-3.407671474970659</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.424722973868152</v>
       </c>
       <c r="E66">
-        <v>-11.37559218261165</v>
+        <v>-10.13283853221266</v>
       </c>
       <c r="F66">
-        <v>-1.352801154187561</v>
+        <v>-0.8786105181290118</v>
       </c>
       <c r="G66">
-        <v>-5.067211537806373</v>
+        <v>-3.198113942334793</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.2473678567185991</v>
       </c>
       <c r="E67">
-        <v>-10.91747363809968</v>
+        <v>-10.10485709131927</v>
       </c>
       <c r="F67">
-        <v>-1.123904188343793</v>
+        <v>-1.215437957985736</v>
       </c>
       <c r="G67">
-        <v>-4.312867320682501</v>
+        <v>-3.457726923524439</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.07183550699243132</v>
       </c>
       <c r="E68">
-        <v>-10.30154230289441</v>
+        <v>-9.359252902904359</v>
       </c>
       <c r="F68">
-        <v>-1.084801933462045</v>
+        <v>-1.331389513559999</v>
       </c>
       <c r="G68">
-        <v>-4.896963422903813</v>
+        <v>-3.56501839390668</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.1015283308062405</v>
       </c>
       <c r="E69">
-        <v>-10.74383383074957</v>
+        <v>-9.896053683299595</v>
       </c>
       <c r="F69">
-        <v>-1.367636386004297</v>
+        <v>-0.6999797146545208</v>
       </c>
       <c r="G69">
-        <v>-4.687150978261423</v>
+        <v>-2.91958781447929</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.2720005952609533</v>
       </c>
       <c r="E70">
-        <v>-9.713479196732351</v>
+        <v>-10.97831368639273</v>
       </c>
       <c r="F70">
-        <v>-1.122273132927681</v>
+        <v>-1.311457337113837</v>
       </c>
       <c r="G70">
-        <v>-5.265920412710048</v>
+        <v>-3.685909585364245</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.4371332203680246</v>
       </c>
       <c r="E71">
-        <v>-11.41785643052524</v>
+        <v>-10.11027767470645</v>
       </c>
       <c r="F71">
-        <v>-1.628395675629345</v>
+        <v>-1.327607187998817</v>
       </c>
       <c r="G71">
-        <v>-4.851367279191431</v>
+        <v>-3.596173937976761</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5956761739770099</v>
       </c>
       <c r="E72">
-        <v>-11.57202379964236</v>
+        <v>-9.571303226787531</v>
       </c>
       <c r="F72">
-        <v>-1.577515693014594</v>
+        <v>-1.533615534135831</v>
       </c>
       <c r="G72">
-        <v>-3.433063359256869</v>
+        <v>-3.37963777534411</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.7457038249084612</v>
       </c>
       <c r="E73">
-        <v>-8.990829843062322</v>
+        <v>-9.935831798982973</v>
       </c>
       <c r="F73">
-        <v>-1.576796670108964</v>
+        <v>-1.902079153472871</v>
       </c>
       <c r="G73">
-        <v>-3.563508785140772</v>
+        <v>-2.91713470023469</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8833688620178081</v>
       </c>
       <c r="E74">
-        <v>-10.81433764257499</v>
+        <v>-11.21877565620003</v>
       </c>
       <c r="F74">
-        <v>-1.89670553413091</v>
+        <v>-1.924962802975207</v>
       </c>
       <c r="G74">
-        <v>-4.439972406117279</v>
+        <v>-3.408360068442827</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.005209932629499</v>
       </c>
       <c r="E75">
-        <v>-11.58887425142491</v>
+        <v>-11.04242782139333</v>
       </c>
       <c r="F75">
-        <v>-1.848054688197093</v>
+        <v>-1.658952492383813</v>
       </c>
       <c r="G75">
-        <v>-4.048828140106849</v>
+        <v>-3.182657005211936</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.107414611870264</v>
       </c>
       <c r="E76">
-        <v>-11.1469087736983</v>
+        <v>-11.01930996158417</v>
       </c>
       <c r="F76">
-        <v>-1.843257612567481</v>
+        <v>-2.059906337993455</v>
       </c>
       <c r="G76">
-        <v>-5.0824466683781</v>
+        <v>-3.305223332712373</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.185611485356314</v>
       </c>
       <c r="E77">
-        <v>-12.72363285368897</v>
+        <v>-11.82631120059508</v>
       </c>
       <c r="F77">
-        <v>-2.13009473640006</v>
+        <v>-2.036973814814353</v>
       </c>
       <c r="G77">
-        <v>-2.914701449263326</v>
+        <v>-3.234635880724033</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.235354924049974</v>
       </c>
       <c r="E78">
-        <v>-11.76887656475579</v>
+        <v>-12.83987878146587</v>
       </c>
       <c r="F78">
-        <v>-1.233183244488506</v>
+        <v>-2.274359889802011</v>
       </c>
       <c r="G78">
-        <v>-3.68470785733349</v>
+        <v>-3.194935818617092</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.252727370361035</v>
       </c>
       <c r="E79">
-        <v>-13.36783998059813</v>
+        <v>-13.59218963988613</v>
       </c>
       <c r="F79">
-        <v>-2.237838827747386</v>
+        <v>-2.45176222441815</v>
       </c>
       <c r="G79">
-        <v>-3.091021104684909</v>
+        <v>-2.280775015584904</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.234589567499957</v>
       </c>
       <c r="E80">
-        <v>-13.93361846616845</v>
+        <v>-13.16122835399817</v>
       </c>
       <c r="F80">
-        <v>-2.423465193938519</v>
+        <v>-2.340958143884883</v>
       </c>
       <c r="G80">
-        <v>-3.454029044157073</v>
+        <v>-2.830679803476623</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.179513036349944</v>
       </c>
       <c r="E81">
-        <v>-14.25474161500037</v>
+        <v>-13.35277827604862</v>
       </c>
       <c r="F81">
-        <v>-1.838684196136625</v>
+        <v>-2.211032858592794</v>
       </c>
       <c r="G81">
-        <v>-2.918247043535885</v>
+        <v>-2.354358511286285</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.08745033762314</v>
       </c>
       <c r="E82">
-        <v>-15.22542001854451</v>
+        <v>-13.95322675862166</v>
       </c>
       <c r="F82">
-        <v>-2.147729850038259</v>
+        <v>-2.111485462696169</v>
       </c>
       <c r="G82">
-        <v>-3.637108833569849</v>
+        <v>-1.794300280225621</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.9598677949245062</v>
       </c>
       <c r="E83">
-        <v>-15.92520963542382</v>
+        <v>-16.09949701455703</v>
       </c>
       <c r="F83">
-        <v>-2.507954527187055</v>
+        <v>-2.493671816427986</v>
       </c>
       <c r="G83">
-        <v>-3.452718068123522</v>
+        <v>-1.851864046062468</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.8007537725715373</v>
       </c>
       <c r="E84">
-        <v>-17.39334090871055</v>
+        <v>-16.84280073817604</v>
       </c>
       <c r="F84">
-        <v>-2.614391454772763</v>
+        <v>-2.690708115225279</v>
       </c>
       <c r="G84">
-        <v>-2.67861651522128</v>
+        <v>-1.975638722684739</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.6149857476403815</v>
       </c>
       <c r="E85">
-        <v>-17.72023333342824</v>
+        <v>-17.11882934283958</v>
       </c>
       <c r="F85">
-        <v>-2.575671905631109</v>
+        <v>-2.558277846907124</v>
       </c>
       <c r="G85">
-        <v>-2.40702929081609</v>
+        <v>-0.8793019091719968</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4086775961840984</v>
       </c>
       <c r="E86">
-        <v>-19.18479164072292</v>
+        <v>-19.27621247398977</v>
       </c>
       <c r="F86">
-        <v>-2.91448991235676</v>
+        <v>-2.931581616978722</v>
       </c>
       <c r="G86">
-        <v>-2.950531483634858</v>
+        <v>-1.462911361199036</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.1893964681317737</v>
       </c>
       <c r="E87">
-        <v>-20.74047190199994</v>
+        <v>-20.24280166550498</v>
       </c>
       <c r="F87">
-        <v>-3.241786985244275</v>
+        <v>-3.106430923259433</v>
       </c>
       <c r="G87">
-        <v>-2.256111451317334</v>
+        <v>-1.605834233220452</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.03312268811871257</v>
       </c>
       <c r="E88">
-        <v>-21.91912047434634</v>
+        <v>-21.60337262416153</v>
       </c>
       <c r="F88">
-        <v>-2.933955717955145</v>
+        <v>-2.616887325757398</v>
       </c>
       <c r="G88">
-        <v>-3.134425667250294</v>
+        <v>-1.058458702120736</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.2494457795364157</v>
       </c>
       <c r="E89">
-        <v>-22.08949978041093</v>
+        <v>-22.42246941724692</v>
       </c>
       <c r="F89">
-        <v>-2.907085136143135</v>
+        <v>-2.891417395086585</v>
       </c>
       <c r="G89">
-        <v>-1.814312528010515</v>
+        <v>-1.931797168108171</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.4500785894555419</v>
       </c>
       <c r="E90">
-        <v>-23.86491518596214</v>
+        <v>-24.7647591990783</v>
       </c>
       <c r="F90">
-        <v>-2.613501788182156</v>
+        <v>-3.405080566255933</v>
       </c>
       <c r="G90">
-        <v>-2.838419858947439</v>
+        <v>-1.849867787102288</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.6247519978331892</v>
       </c>
       <c r="E91">
-        <v>-24.3597551262023</v>
+        <v>-24.90621967012991</v>
       </c>
       <c r="F91">
-        <v>-2.666967933828448</v>
+        <v>-3.205731465670024</v>
       </c>
       <c r="G91">
-        <v>-2.029302665876326</v>
+        <v>-1.827627542169464</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.7641574852702945</v>
       </c>
       <c r="E92">
-        <v>-25.7410212110739</v>
+        <v>-26.59337964574563</v>
       </c>
       <c r="F92">
-        <v>-3.210975031329744</v>
+        <v>-3.386755422571202</v>
       </c>
       <c r="G92">
-        <v>-2.542910632475475</v>
+        <v>-2.109027223553054</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.8607743820877307</v>
       </c>
       <c r="E93">
-        <v>-28.66250281848632</v>
+        <v>-28.95567169726889</v>
       </c>
       <c r="F93">
-        <v>-3.508537856293772</v>
+        <v>-3.782966036432414</v>
       </c>
       <c r="G93">
-        <v>-2.365839483216477</v>
+        <v>-2.558407296144804</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.9094012611026685</v>
       </c>
       <c r="E94">
-        <v>-30.8906071282143</v>
+        <v>-30.29694909241576</v>
       </c>
       <c r="F94">
-        <v>-3.626820437739513</v>
+        <v>-3.514720790588267</v>
       </c>
       <c r="G94">
-        <v>-2.766140718188531</v>
+        <v>-1.894139712598961</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.9069951750768914</v>
       </c>
       <c r="E95">
-        <v>-32.53287407675499</v>
+        <v>-33.35216785845971</v>
       </c>
       <c r="F95">
-        <v>-3.751614815338661</v>
+        <v>-3.507359917846991</v>
       </c>
       <c r="G95">
-        <v>-3.117492226816922</v>
+        <v>-2.338189806872484</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.8514086389514141</v>
       </c>
       <c r="E96">
-        <v>-34.79261204166354</v>
+        <v>-34.51641135498771</v>
       </c>
       <c r="F96">
-        <v>-3.571615548914746</v>
+        <v>-4.087830091684716</v>
       </c>
       <c r="G96">
-        <v>-3.562028971284717</v>
+        <v>-2.710010418570188</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.7475887160388478</v>
       </c>
       <c r="E97">
-        <v>-36.88790979416857</v>
+        <v>-37.21791101629253</v>
       </c>
       <c r="F97">
-        <v>-3.800843033352231</v>
+        <v>-3.984393510831948</v>
       </c>
       <c r="G97">
-        <v>-4.331472586613205</v>
+        <v>-2.59117507589251</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.5938701131375892</v>
       </c>
       <c r="E98">
-        <v>-39.18294494972992</v>
+        <v>-38.21466890164685</v>
       </c>
       <c r="F98">
-        <v>-3.911889825534518</v>
+        <v>-4.106786451330381</v>
       </c>
       <c r="G98">
-        <v>-4.435993130379075</v>
+        <v>-3.186123146391552</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.402344498870267</v>
       </c>
       <c r="E99">
-        <v>-41.91709264439303</v>
+        <v>-40.68167512188647</v>
       </c>
       <c r="F99">
-        <v>-4.497523213393893</v>
+        <v>-4.108057995293677</v>
       </c>
       <c r="G99">
-        <v>-4.386434263656185</v>
+        <v>-2.976539129391373</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.1661945291111248</v>
       </c>
       <c r="E100">
-        <v>-43.17036367567483</v>
+        <v>-43.58489792209997</v>
       </c>
       <c r="F100">
-        <v>-4.181462944325353</v>
+        <v>-4.645307271522936</v>
       </c>
       <c r="G100">
-        <v>-4.840942371288266</v>
+        <v>-4.330605223681916</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.08980728102194153</v>
       </c>
       <c r="E101">
-        <v>-45.29598409013522</v>
+        <v>-44.8876040398865</v>
       </c>
       <c r="F101">
-        <v>-4.396087139818885</v>
+        <v>-4.463064786172239</v>
       </c>
       <c r="G101">
-        <v>-4.640598086888192</v>
+        <v>-4.10987459985101</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.3940011331867265</v>
       </c>
       <c r="E102">
-        <v>-46.34513415552127</v>
+        <v>-46.74735095264555</v>
       </c>
       <c r="F102">
-        <v>-4.86282578272185</v>
+        <v>-4.715142785415948</v>
       </c>
       <c r="G102">
-        <v>-5.35689420412922</v>
+        <v>-3.826081394042526</v>
       </c>
     </row>
   </sheetData>
